--- a/Numerical methods/LW9/LW9.xlsx
+++ b/Numerical methods/LW9/LW9.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\studies\Numerical methods\LW9\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F53C24E-6EF2-493D-9467-42D8A406D20B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BD4DF7E-B069-4583-9979-CD6945B46264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -86,12 +86,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -482,19 +481,19 @@
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
-      <c r="I6" s="2">
+      <c r="I6">
         <f>B10</f>
         <v>-0.69298000000000004</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6">
         <f t="shared" ref="J6:K6" si="0">C10</f>
         <v>0.41626999999999997</v>
       </c>
-      <c r="K6" s="2">
+      <c r="K6">
         <f t="shared" si="0"/>
         <v>0.79378000000000004</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6">
         <f>G10</f>
         <v>-3.2713999999999999</v>
       </c>
@@ -530,7 +529,7 @@
         <f t="shared" si="1"/>
         <v>2.5100000000000001E-3</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7">
         <f>G11</f>
         <v>-5.9146799999999997</v>
       </c>
